--- a/DBP_master_corpus.xlsx
+++ b/DBP_master_corpus.xlsx
@@ -1228,10 +1228,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
@@ -1239,7 +1243,11 @@
           <t>Examines neighbour-notification procedure in planning applications</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Brand C.M.</t>
@@ -1754,10 +1762,14 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr">
@@ -1765,7 +1777,11 @@
           <t>Examines development-agreement/permitting negotiation practice</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Fulton W.</t>
@@ -2232,10 +2248,14 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr">
@@ -2243,7 +2263,11 @@
           <t>Examines building-permit procedures/impediments in Cameroon</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Njoh A.J.</t>
@@ -2319,10 +2343,14 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr">
@@ -2330,7 +2358,11 @@
           <t>Studies development-control negotiation and delay</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Glasson B.; Booth P.</t>
@@ -2509,10 +2541,14 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr">
@@ -2520,7 +2556,11 @@
           <t>Overview of planning-permission-based land-use system</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Grant M.</t>
@@ -3791,10 +3831,14 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="inlineStr">
@@ -3802,7 +3846,11 @@
           <t>Examines public concern's materiality in planning decisions</t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
           <t>Gilles J.</t>
@@ -4210,10 +4258,14 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr">
@@ -4221,7 +4273,11 @@
           <t>On planning-application processing targets (no abstract)</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L43" s="3" t="n"/>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -13168,10 +13224,14 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H145" s="3" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr"/>
       <c r="J145" s="3" t="inlineStr">
@@ -13179,7 +13239,11 @@
           <t>Studies rural construction planning permission system</t>
         </is>
       </c>
-      <c r="K145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
           <t>Dai, CL</t>
@@ -22507,10 +22571,14 @@
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G246" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H246" s="3" t="inlineStr"/>
       <c r="I246" s="3" t="inlineStr"/>
       <c r="J246" s="3" t="inlineStr">
@@ -22518,7 +22586,11 @@
           <t>Automated BIM building rules compliance for permits</t>
         </is>
       </c>
-      <c r="K246" s="3" t="inlineStr"/>
+      <c r="K246" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
           <t>Abdelalim A.M.; Elbeltagi E.E.; Abdelgawad M.</t>
@@ -23706,10 +23778,14 @@
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>— not read (no PDF)</t>
-        </is>
-      </c>
-      <c r="G259" s="6" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G259" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H259" s="3" t="inlineStr"/>
       <c r="I259" s="3" t="inlineStr"/>
       <c r="J259" s="3" t="inlineStr">
@@ -23717,7 +23793,11 @@
           <t>Improving building permit grant deployment, Can Tho</t>
         </is>
       </c>
-      <c r="K259" s="3" t="inlineStr"/>
+      <c r="K259" s="3" t="inlineStr">
+        <is>
+          <t>Excluded — no accessible full text to verify against scope.</t>
+        </is>
+      </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
           <t>Thanh M.N.T.; Ngoc V.N.T.</t>
@@ -31832,12 +31912,8 @@
           <t>DBP systematic map — corpus, screening &amp; full-text extraction</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
